--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BK Olympic</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>BK Olympic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1588,7 +1588,515 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IRT Tanger</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wydad Casablanca</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -875,212 +875,212 @@
         <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -884,7 +884,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1123,218 +1123,218 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1377,218 +1377,218 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
@@ -1144,7 +1144,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.15</v>
@@ -1416,7 +1416,7 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>1.92</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1888,19 +1888,19 @@
         <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
@@ -1909,194 +1909,448 @@
         <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -860,7 +860,7 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
         <v>1.06</v>
@@ -1150,7 +1150,7 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
@@ -1416,7 +1416,7 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="G5" t="n">
         <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="I5" t="n">
         <v>2.16</v>
       </c>
       <c r="J5" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1885,10 +1885,10 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,34 +1897,34 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.02</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
         <v>1.06</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J4" t="n">
         <v>1.06</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="n">
         <v>2.16</v>
       </c>
       <c r="J5" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,10 +1643,10 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1670,7 +1670,7 @@
         <v>1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1900,19 +1900,19 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,7 +1921,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>2.16</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
@@ -2139,7 +2139,7 @@
         <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2350,7 +2350,515 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Club ABB</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:29:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Louisville FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>970</v>
@@ -890,13 +890,13 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>970</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>970</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>970</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>2.16</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
@@ -1646,19 +1646,19 @@
         <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
         <v>1.04</v>
@@ -1906,13 +1906,13 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G9" t="n">
         <v>4.1</v>
@@ -2665,13 +2665,13 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
         <v>2.84</v>
@@ -2680,7 +2680,7 @@
         <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V9" t="n">
         <v>1.98</v>
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE9" t="n">
         <v>19.5</v>
@@ -2722,7 +2722,7 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
         <v>80</v>
@@ -2731,13 +2731,13 @@
         <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
         <v>11.5</v>
@@ -2767,7 +2767,7 @@
         <v>16.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY9" t="n">
         <v>14.5</v>
@@ -2779,7 +2779,7 @@
         <v>26</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
         <v>38</v>
@@ -2788,77 +2788,77 @@
         <v>42</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG9" t="n">
         <v>10</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
         <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="n">
         <v>970</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1413,10 +1413,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
         <v>25</v>
@@ -1631,10 +1631,10 @@
         <v>2.16</v>
       </c>
       <c r="J5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1652,13 +1652,13 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>970</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>1.97</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="I7" t="n">
         <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2178,7 +2178,7 @@
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
         <v>970</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J8" t="n">
         <v>1.04</v>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.14</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G9" t="n">
         <v>4.1</v>
@@ -2665,10 +2665,10 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -2683,7 +2683,7 @@
         <v>2.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W9" t="n">
         <v>1.32</v>
@@ -2701,7 +2701,7 @@
         <v>24</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
         <v>34</v>
@@ -2725,7 +2725,7 @@
         <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK9" t="n">
         <v>46</v>
@@ -2734,13 +2734,13 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
         <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
@@ -2767,7 +2767,7 @@
         <v>16.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
         <v>14.5</v>
@@ -2779,7 +2779,7 @@
         <v>26</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
         <v>38</v>
@@ -2788,10 +2788,10 @@
         <v>42</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG9" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>6</v>
       </c>
       <c r="BP9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
         <v>8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,103 +857,103 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.23</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>970</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>2.52</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.47</v>
+        <v>2.68</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.47</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -965,64 +965,64 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,55 +1102,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BK Olympic</t>
+          <t>TSV Graf'stein</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Dellach/Gail</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.09</v>
       </c>
-      <c r="G3" t="n">
-        <v>970</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I3" t="n">
-        <v>970</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K3" t="n">
-        <v>950</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.18</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>BK Olympic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.16</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>2.06</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="I6" t="n">
-        <v>970</v>
+        <v>2.16</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>2.88</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.11</v>
+        <v>5.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR7" t="n">
         <v>2.02</v>
       </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -2367,33 +2367,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club ABB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1.09</v>
       </c>
       <c r="G8" t="n">
-        <v>970</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>110</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.09</v>
-      </c>
-      <c r="I8" t="n">
-        <v>970</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,261 +2604,515 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Club ABB</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>970</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>970</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-02 06:50:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Birmingham Legion FC</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Louisville FC</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.9</v>
       </c>
-      <c r="G9" t="n">
+      <c r="K10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.1</v>
       </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="O10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.67</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>2.22</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="V10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>10</v>
       </c>
-      <c r="AD9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AR10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW10" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AX10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB10" t="n">
         <v>55</v>
       </c>
-      <c r="AM9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="BC10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="BN10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV10" t="n">
         <v>15</v>
       </c>
-      <c r="AU9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO9" t="n">
+      <c r="BW10" t="n">
         <v>6</v>
       </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BX10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="CA9" t="n">
+      <c r="BZ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA10" t="n">
         <v>6.8</v>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-02 04:43:26</t>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,37 +857,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
         <v>2.68</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.1</v>
@@ -905,10 +905,10 @@
         <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -947,10 +947,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
         <v>85</v>
@@ -965,122 +965,122 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.3</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AU2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1.92</v>
       </c>
-      <c r="AS2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AY2" t="n">
         <v>2.5</v>
       </c>
-      <c r="AW2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>2.98</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1141,13 +1141,13 @@
         <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
         <v>1.01</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
         <v>1.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1873,46 +1873,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
         <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,43 +1921,43 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -2029,74 +2029,74 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2127,67 +2127,67 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
         <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="X7" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
         <v>130</v>
@@ -2211,64 +2211,64 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
         <v>130</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AR7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS7" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS7" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
         <v>6.2</v>
@@ -2277,22 +2277,22 @@
         <v>6.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="BF7" t="n">
         <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2381,112 +2381,112 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP8" t="n">
         <v>1.03</v>
@@ -2537,74 +2537,74 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2635,112 +2635,112 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.74</v>
       </c>
       <c r="G9" t="n">
-        <v>970</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>970</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP9" t="n">
         <v>1.03</v>
@@ -2791,74 +2791,74 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="n">
         <v>2.08</v>
@@ -2907,7 +2907,7 @@
         <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2919,7 +2919,7 @@
         <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>1.79</v>
@@ -2931,10 +2931,10 @@
         <v>2.92</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.83</v>
@@ -2946,7 +2946,7 @@
         <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
@@ -2958,7 +2958,7 @@
         <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
@@ -2970,10 +2970,10 @@
         <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>32</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
         <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -884,13 +884,13 @@
         <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -905,10 +905,10 @@
         <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,7 +917,7 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -941,16 +941,16 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK2" t="n">
         <v>46</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>44</v>
       </c>
       <c r="AL2" t="n">
         <v>85</v>
@@ -965,61 +965,61 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX2" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.72</v>
-      </c>
       <c r="AY2" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.08</v>
+        <v>3.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
         <v>2.2</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,19 +1046,19 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>970</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>2.54</v>
       </c>
       <c r="I4" t="n">
-        <v>970</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>1.17</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.06</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>1.15</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.88</v>
@@ -1888,91 +1888,91 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W6" t="n">
         <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -1981,122 +1981,122 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU6" t="n">
         <v>3.2</v>
       </c>
-      <c r="BI6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
         <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
         <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
         <v>1.81</v>
       </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>6</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>6</v>
       </c>
-      <c r="BA7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
         <v>4.2</v>
@@ -2393,10 +2393,10 @@
         <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>1.23</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.44</v>
@@ -2423,7 +2423,7 @@
         <v>2.06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U8" t="n">
         <v>2.36</v>
@@ -2432,7 +2432,7 @@
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
@@ -2447,10 +2447,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
         <v>23</v>
@@ -2459,22 +2459,22 @@
         <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
         <v>29</v>
@@ -2483,128 +2483,128 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
         <v>42</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I9" t="n">
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4.9</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.17</v>
@@ -2677,13 +2677,13 @@
         <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
         <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
         <v>2.04</v>
@@ -2692,7 +2692,7 @@
         <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z9" t="n">
         <v>44</v>
@@ -2701,37 +2701,37 @@
         <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
         <v>75</v>
@@ -2743,122 +2743,122 @@
         <v>40</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="n">
         <v>4.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="BP9" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BR9" t="n">
         <v>22</v>
       </c>
       <c r="BS9" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BT9" t="n">
         <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
         <v>15</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
         <v>2.08</v>
@@ -2904,7 +2904,7 @@
         <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2919,16 +2919,16 @@
         <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
         <v>1.66</v>
@@ -2937,7 +2937,7 @@
         <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W10" t="n">
         <v>1.36</v>
@@ -2955,7 +2955,7 @@
         <v>28</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9</v>
@@ -2964,19 +2964,19 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
         <v>70</v>
@@ -2985,19 +2985,19 @@
         <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
         <v>14.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>7.8</v>
@@ -3018,7 +3018,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX10" t="n">
         <v>22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -902,13 +902,13 @@
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -941,7 +941,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -968,13 +968,13 @@
         <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AT2" t="n">
         <v>5.6</v>
@@ -983,104 +983,104 @@
         <v>5.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AZ2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
         <v>3.9</v>
       </c>
-      <c r="BA2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.26</v>
@@ -1389,22 +1389,22 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>1.86</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1413,10 +1413,10 @@
         <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
         <v>26</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>6.2</v>
@@ -1652,7 +1652,7 @@
         <v>2.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.64</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
         <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1915,34 +1915,34 @@
         <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
         <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,10 +1951,10 @@
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AG6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
@@ -1981,58 +1981,58 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AY6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5.2</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BC6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
         <v>5.3</v>
       </c>
-      <c r="BA6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.84</v>
-      </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.1</v>
@@ -2044,59 +2044,59 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.51</v>
@@ -2151,13 +2151,13 @@
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
         <v>1.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
         <v>2.78</v>
@@ -2172,13 +2172,13 @@
         <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
         <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X7" t="n">
         <v>9.4</v>
@@ -2187,10 +2187,10 @@
         <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
         <v>7.6</v>
@@ -2199,7 +2199,7 @@
         <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
         <v>120</v>
@@ -2208,7 +2208,7 @@
         <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>34</v>
@@ -2229,128 +2229,128 @@
         <v>310</v>
       </c>
       <c r="AN7" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
         <v>5.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA7" t="n">
+      <c r="BC7" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BD7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.62</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>6.6</v>
+        <v>2.18</v>
       </c>
       <c r="BN7" t="n">
         <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU7" t="n">
         <v>5.9</v>
       </c>
-      <c r="BT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>1.23</v>
@@ -2405,19 +2405,19 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
         <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
         <v>2.06</v>
@@ -2429,10 +2429,10 @@
         <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
@@ -2471,13 +2471,13 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
         <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2489,58 +2489,58 @@
         <v>42</v>
       </c>
       <c r="AP8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>1.99</v>
       </c>
       <c r="BF8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.24</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="X9" t="n">
         <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>9</v>
       </c>
-      <c r="AO9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="AZ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="n">
         <v>4.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR9" t="n">
         <v>22</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
         <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>15</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>3.35</v>
       </c>
       <c r="G10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.9</v>
@@ -2919,13 +2919,13 @@
         <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
         <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
         <v>2.96</v>
@@ -2937,10 +2937,10 @@
         <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
         <v>17</v>
@@ -2955,7 +2955,7 @@
         <v>28</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
         <v>9</v>
@@ -2964,7 +2964,7 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>30</v>
@@ -2982,22 +2982,22 @@
         <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO10" t="n">
         <v>14.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>10</v>
@@ -3060,31 +3060,31 @@
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO10" t="n">
         <v>5.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
         <v>5.2</v>
@@ -3096,23 +3096,23 @@
         <v>15</v>
       </c>
       <c r="BW10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX10" t="n">
         <v>27</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>22</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -860,19 +860,19 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
         <v>3.45</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -881,34 +881,34 @@
         <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.56</v>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T2" t="n">
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -968,55 +968,55 @@
         <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU2" t="n">
         <v>5.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.24</v>
+        <v>1.69</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
         <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="I3" t="n">
         <v>44</v>
       </c>
       <c r="J3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.26</v>
@@ -1389,67 +1389,67 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1458,137 +1458,137 @@
         <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.8</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI4" t="n">
         <v>3.15</v>
       </c>
-      <c r="AV4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.68</v>
-      </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BN4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP4" t="n">
+      <c r="BX4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>19.5</v>
       </c>
-      <c r="BQ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>21</v>
-      </c>
       <c r="CA4" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.64</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
         <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
         <v>13.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>13</v>
       </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>19.5</v>
       </c>
-      <c r="AL5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="BE5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG5" t="n">
+      <c r="BH5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4.1</v>
       </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.21</v>
+        <v>5.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.17</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.15</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.14</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.17</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
         <v>1.93</v>
@@ -1888,7 +1888,7 @@
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1900,7 +1900,7 @@
         <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
         <v>1.67</v>
@@ -1912,7 +1912,7 @@
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
         <v>1.95</v>
@@ -1930,7 +1930,7 @@
         <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>970</v>
@@ -1984,55 +1984,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>4.5</v>
       </c>
       <c r="AW6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.1</v>
@@ -2050,13 +2050,13 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2068,13 +2068,13 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="BT6" t="n">
         <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -2172,7 +2172,7 @@
         <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
         <v>1.23</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2328,7 +2328,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -2384,28 +2384,28 @@
         <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H8" t="n">
         <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.23</v>
       </c>
       <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.15</v>
@@ -2414,34 +2414,34 @@
         <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
         <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2453,10 +2453,10 @@
         <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
@@ -2468,10 +2468,10 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
         <v>970</v>
@@ -2480,131 +2480,131 @@
         <v>27</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>2.24</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AY8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.24</v>
@@ -2662,16 +2662,16 @@
         <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
         <v>2.38</v>
@@ -2680,16 +2680,16 @@
         <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y9" t="n">
         <v>24</v>
@@ -2710,10 +2710,10 @@
         <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2722,13 +2722,13 @@
         <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL9" t="n">
         <v>28</v>
@@ -2737,64 +2737,64 @@
         <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO9" t="n">
         <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>5.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
         <v>13.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG9" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.8</v>
       </c>
       <c r="BH9" t="n">
         <v>4.7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -2889,127 +2889,127 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
         <v>2.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J10" t="n">
         <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W10" t="n">
         <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
         <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
         <v>7.8</v>
@@ -3018,55 +3018,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
         <v>55</v>
       </c>
       <c r="BC10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD10" t="n">
         <v>38</v>
       </c>
       <c r="BE10" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="BF10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>7.4</v>
@@ -3075,16 +3075,16 @@
         <v>5.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>5.2</v>
@@ -3093,26 +3093,26 @@
         <v>4</v>
       </c>
       <c r="BV10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW10" t="n">
         <v>6.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA10" t="n">
         <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,112 +848,112 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>SV Anthering</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>SV Burmoos</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>210</v>
       </c>
       <c r="H2" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>3.95</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>1.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.72</v>
+        <v>1.13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>5.6</v>
+        <v>1.13</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -965,129 +965,129 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TSV Graf'stein</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dellach/Gail</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>1.08</v>
       </c>
-      <c r="G3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I3" t="n">
-        <v>44</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="K3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BK Olympic</t>
+          <t>FC Hard</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>SC Rothis</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>210</v>
       </c>
       <c r="H4" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>210</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>110</v>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>1.08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>1.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>TSV Graf'stein</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Dellach/Gail</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.74</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.24</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
         <v>1.03</v>
       </c>
-      <c r="N5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X5" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>BK Olympic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH6" t="n">
         <v>4.5</v>
       </c>
-      <c r="G6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="BI6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR6" t="n">
         <v>26</v>
       </c>
-      <c r="AF6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="BS6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV6" t="n">
         <v>20</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
       </c>
       <c r="BW6" t="n">
         <v>6.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Dellach/Gail</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.16</v>
+        <v>44</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS8" t="n">
         <v>4.6</v>
       </c>
-      <c r="I8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="AT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.6</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X8" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="AZ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,498 +2621,1260 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club ABB</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="T9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
         <v>4.5</v>
       </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="AW9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5.5</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="BF9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG9" t="n">
+      <c r="BU9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BH9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Raja Casablanca</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RSB Berkane</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:24:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:24:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Club ABB</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:24:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Birmingham Legion FC</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Louisville FC</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>3.45</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G13" t="n">
         <v>3.75</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H13" t="n">
         <v>2.1</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I13" t="n">
         <v>2.18</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>3.9</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>3.95</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.06</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N13" t="n">
         <v>3.9</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O13" t="n">
         <v>1.28</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P13" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q13" t="n">
         <v>1.83</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S13" t="n">
         <v>3.15</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="T13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.16</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V13" t="n">
         <v>1.85</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W13" t="n">
         <v>1.37</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X13" t="n">
         <v>16</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y13" t="n">
         <v>11</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA13" t="n">
         <v>27</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB13" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE13" t="n">
         <v>23</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF13" t="n">
         <v>27</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG13" t="n">
         <v>15</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH13" t="n">
         <v>20</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI13" t="n">
         <v>36</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ13" t="n">
         <v>70</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK13" t="n">
         <v>42</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL13" t="n">
         <v>50</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AM13" t="n">
         <v>85</v>
       </c>
-      <c r="AN10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="AN13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO13" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR13" t="n">
         <v>12</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS13" t="n">
         <v>23</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AT13" t="n">
         <v>13</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AU13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AV13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AW13" t="n">
         <v>8.6</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AX13" t="n">
         <v>24</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AY13" t="n">
         <v>13</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AZ13" t="n">
         <v>15</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BA13" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB13" t="n">
         <v>55</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BC13" t="n">
         <v>34</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BD13" t="n">
         <v>38</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BE13" t="n">
         <v>12</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BF13" t="n">
         <v>10</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BG13" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BH13" t="n">
         <v>3.75</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BI13" t="n">
         <v>3</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BJ13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BK13" t="n">
         <v>5</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>9.6</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BN13" t="n">
         <v>7.4</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BO13" t="n">
         <v>5.6</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BP13" t="n">
         <v>32</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BQ13" t="n">
         <v>7.8</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="BT13" t="n">
         <v>5.2</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="BU13" t="n">
         <v>4</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="BV13" t="n">
         <v>15.5</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="BW13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="BX13" t="n">
         <v>28</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="BY13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="BZ13" t="n">
         <v>23</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CA13" t="n">
         <v>7.2</v>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:18:07</t>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>1.13</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1013,10 +1013,10 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
         <v>3.75</v>
@@ -1126,25 +1126,25 @@
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1153,40 +1153,40 @@
         <v>5.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.69</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1195,22 +1195,22 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
@@ -1219,64 +1219,64 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.82</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.13</v>
+        <v>2.42</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.08</v>
+        <v>2.44</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.12</v>
+        <v>2.36</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.12</v>
+        <v>2.38</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Hard</t>
+          <t>SV Spittal/Drau</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SC Rothis</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>210</v>
+        <v>600</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>210</v>
+        <v>870</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,34 +1389,34 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -1605,72 +1605,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TSV Graf'stein</t>
+          <t>FC Hard</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dellach/Gail</t>
+          <t>SC Rothis</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>990</v>
       </c>
       <c r="H5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="n">
         <v>44</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,129 +1727,129 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BK Olympic</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Dellach/Gail</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>1.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>600</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>1.08</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>870</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>1.08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="BG6" t="n">
-        <v>14</v>
+        <v>1.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TSV Grafenstein</t>
+          <t>BK Olympic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dellach/Gail</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>2.74</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
         <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
@@ -2414,7 +2414,7 @@
         <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R8" t="n">
         <v>1.6</v>
@@ -2423,52 +2423,52 @@
         <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y8" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AA8" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
         <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
         <v>21</v>
@@ -2477,10 +2477,10 @@
         <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>7</v>
@@ -2489,70 +2489,70 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>18</v>
       </c>
       <c r="AR8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AW8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="n">
         <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,7 +2564,7 @@
         <v>4.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
         <v>1.98</v>
@@ -2689,58 +2689,58 @@
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AM9" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
         <v>8.199999999999999</v>
@@ -2752,7 +2752,7 @@
         <v>9.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2761,40 +2761,40 @@
         <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.1</v>
@@ -2806,7 +2806,7 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,7 +2818,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Sacachispas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>2.14</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.66</v>
       </c>
-      <c r="H11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.32</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>38</v>
       </c>
-      <c r="Y11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>970</v>
-      </c>
       <c r="AK11" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI11" t="n">
         <v>2.24</v>
       </c>
-      <c r="AS11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="BJ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO11" t="n">
         <v>4</v>
       </c>
-      <c r="AU11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>2.14</v>
       </c>
-      <c r="AW11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6</v>
+        <v>2.14</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>6</v>
+        <v>2.18</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -3383,498 +3383,752 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club ABB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>4.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>4.4</v>
-      </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>1.02</v>
       </c>
       <c r="O12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="T12" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X12" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW12" t="n">
         <v>2.66</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="AX12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY12" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="AZ12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>6</v>
       </c>
-      <c r="AX12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Club ABB</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:31:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Birmingham Legion FC</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Louisville FC</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>3.45</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" t="n">
         <v>3.75</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
         <v>2.1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>2.18</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>3.9</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>3.95</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>1.32</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>1.06</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="N14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.28</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P14" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q14" t="n">
         <v>1.83</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.15</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>1.71</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>2.16</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V14" t="n">
         <v>1.85</v>
       </c>
-      <c r="W13" t="n">
+      <c r="W14" t="n">
         <v>1.37</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X14" t="n">
         <v>16</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y14" t="n">
         <v>11</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z14" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA14" t="n">
         <v>27</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AB14" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE14" t="n">
         <v>23</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AF14" t="n">
         <v>27</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AG14" t="n">
         <v>15</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AH14" t="n">
         <v>20</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AI14" t="n">
         <v>36</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AJ14" t="n">
         <v>70</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK14" t="n">
         <v>42</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL14" t="n">
         <v>50</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AM14" t="n">
         <v>85</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD14" t="n">
         <v>38</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="BE14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV14" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="BW14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>23</v>
       </c>
-      <c r="AT13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA13" t="n">
+      <c r="CA14" t="n">
         <v>7.2</v>
       </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-02 17:24:55</t>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="I2" t="n">
         <v>44</v>
@@ -881,19 +881,19 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
         <v>1.13</v>
@@ -902,7 +902,7 @@
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
@@ -911,58 +911,58 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
         <v>3.75</v>
@@ -1135,7 +1135,7 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O3" t="n">
         <v>1.54</v>
@@ -1159,7 +1159,7 @@
         <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
         <v>1.69</v>
@@ -1180,7 +1180,7 @@
         <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
@@ -1225,10 +1225,10 @@
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="AT3" t="n">
         <v>4.2</v>
@@ -1240,7 +1240,7 @@
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1249,46 +1249,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="n">
         <v>2.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>2.36</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>2.38</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>990</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.07</v>
+        <v>1.91</v>
       </c>
       <c r="I5" t="n">
         <v>44</v>
@@ -1634,7 +1634,7 @@
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1670,7 +1670,7 @@
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1682,13 +1682,13 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1778,7 +1778,7 @@
         <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
         <v>2.74</v>
@@ -2136,7 +2136,7 @@
         <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -2145,7 +2145,7 @@
         <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
@@ -2175,7 +2175,7 @@
         <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>1.58</v>
@@ -2211,7 +2211,7 @@
         <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI7" t="n">
         <v>34</v>
@@ -2220,7 +2220,7 @@
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>32</v>
@@ -2229,37 +2229,37 @@
         <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AQ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2277,13 +2277,13 @@
         <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
         <v>14</v>
@@ -2292,7 +2292,7 @@
         <v>4.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
@@ -2316,7 +2316,7 @@
         <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BR7" t="n">
         <v>26</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
         <v>4.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
         <v>4.9</v>
@@ -2546,7 +2546,7 @@
         <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -2659,28 +2659,28 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>1.94</v>
@@ -2743,7 +2743,7 @@
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.4</v>
@@ -2770,28 +2770,28 @@
         <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
         <v>6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
         <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="I10" t="n">
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2928,7 +2928,7 @@
         <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -3164,7 +3164,7 @@
         <v>1.51</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
         <v>2.42</v>
@@ -3185,16 +3185,16 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X11" t="n">
         <v>9.4</v>
@@ -3221,10 +3221,10 @@
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
         <v>75</v>
@@ -3233,7 +3233,7 @@
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>44</v>
@@ -3251,28 +3251,28 @@
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.8</v>
       </c>
       <c r="AR11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW11" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
         <v>5.6</v>
@@ -3281,28 +3281,28 @@
         <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
         <v>2.6</v>
@@ -3326,7 +3326,7 @@
         <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3344,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H12" t="n">
         <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.23</v>
@@ -3421,13 +3421,13 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
         <v>1.43</v>
@@ -3436,13 +3436,13 @@
         <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
         <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
         <v>1.19</v>
@@ -3505,13 +3505,13 @@
         <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="AS12" t="n">
         <v>2.24</v>
@@ -3520,13 +3520,13 @@
         <v>4.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AX12" t="n">
         <v>4.3</v>
@@ -3535,10 +3535,10 @@
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="BB12" t="n">
         <v>4.7</v>
@@ -3550,13 +3550,13 @@
         <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="BF12" t="n">
         <v>3.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="n">
         <v>18</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -3675,40 +3675,40 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
         <v>2.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="U13" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
         <v>48</v>
@@ -3717,43 +3717,43 @@
         <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
         <v>55</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AO13" t="n">
         <v>32</v>
@@ -3765,49 +3765,49 @@
         <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF13" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.8</v>
       </c>
       <c r="BG13" t="n">
         <v>6.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
         <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
         <v>2.02</v>
@@ -3947,10 +3947,10 @@
         <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
         <v>1.85</v>
@@ -3959,13 +3959,13 @@
         <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
         <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
         <v>27</v>
@@ -4058,10 +4058,10 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
         <v>11.5</v>
@@ -4070,7 +4070,7 @@
         <v>3.75</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.800000000000001</v>
@@ -4082,10 +4082,10 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO14" t="n">
         <v>5.6</v>
@@ -4106,29 +4106,29 @@
         <v>5.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX14" t="n">
         <v>28</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>23</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -860,10 +860,10 @@
         <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="I2" t="n">
         <v>44</v>
@@ -881,19 +881,19 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
         <v>1.13</v>
@@ -908,7 +908,7 @@
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>500</v>
@@ -965,52 +965,52 @@
         <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.12</v>
@@ -1159,7 +1159,7 @@
         <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.69</v>
@@ -1180,10 +1180,10 @@
         <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1219,16 +1219,16 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="AT3" t="n">
         <v>4.2</v>
@@ -1240,7 +1240,7 @@
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1249,28 +1249,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>2.76</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I5" t="n">
-        <v>44</v>
+        <v>2.26</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.79</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>900</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AK5" t="n">
         <v>42</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -1981,58 +1981,58 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
         <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>2.74</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
         <v>1.73</v>
@@ -2453,7 +2453,7 @@
         <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
         <v>5.1</v>
@@ -2647,10 +2647,10 @@
         <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.48</v>
@@ -2677,7 +2677,7 @@
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
         <v>1.87</v>
@@ -2686,7 +2686,7 @@
         <v>1.94</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
         <v>90</v>
@@ -2716,7 +2716,7 @@
         <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH9" t="n">
         <v>500</v>
@@ -2782,7 +2782,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BD9" t="n">
         <v>9</v>
@@ -2791,7 +2791,7 @@
         <v>6.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
         <v>6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
         <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
         <v>5.5</v>
@@ -3158,7 +3158,7 @@
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -3167,16 +3167,16 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3185,16 +3185,16 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
         <v>9.4</v>
@@ -3209,19 +3209,19 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
         <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
         <v>11.5</v>
@@ -3233,7 +3233,7 @@
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="n">
         <v>44</v>
@@ -3257,22 +3257,22 @@
         <v>5.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AX11" t="n">
         <v>5.6</v>
@@ -3281,28 +3281,28 @@
         <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>2.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
@@ -3448,7 +3448,7 @@
         <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
         <v>500</v>
@@ -3469,7 +3469,7 @@
         <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
@@ -3511,7 +3511,7 @@
         <v>2.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="AS12" t="n">
         <v>2.24</v>
@@ -3550,7 +3550,7 @@
         <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="BF12" t="n">
         <v>3.25</v>
@@ -3577,7 +3577,7 @@
         <v>1.84</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO12" t="n">
         <v>3.05</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
         <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK13" t="n">
         <v>18</v>
@@ -3759,16 +3759,16 @@
         <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
@@ -3783,7 +3783,7 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
         <v>7</v>
@@ -3792,13 +3792,13 @@
         <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
         <v>21</v>
@@ -3810,7 +3810,7 @@
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -3929,10 +3929,10 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
         <v>2.02</v>
@@ -3941,7 +3941,7 @@
         <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
         <v>3.15</v>
@@ -4025,7 +4025,7 @@
         <v>23</v>
       </c>
       <c r="AT14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU14" t="n">
         <v>7.8</v>
@@ -4034,19 +4034,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX14" t="n">
         <v>24</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>55</v>
@@ -4058,10 +4058,10 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>1.84</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>2.18</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AB2" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AC2" t="n">
-        <v>95</v>
+        <v>14.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.05</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1177,16 +1177,16 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8</v>
-      </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1210,7 +1210,7 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
@@ -1219,61 +1219,61 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.76</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI3" t="n">
         <v>2.2</v>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.42</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.28</v>
+        <v>1.49</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.34</v>
+        <v>1.51</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.36</v>
+        <v>1.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1401,16 +1401,16 @@
         <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
         <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -1619,73 +1619,73 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H5" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="I5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
         <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
         <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
@@ -1697,22 +1697,22 @@
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>110</v>
@@ -1721,73 +1721,73 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="n">
         <v>4.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK5" t="n">
         <v>4.1</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
         <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT5" t="n">
         <v>5.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
         <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BZ5" t="n">
         <v>18</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
         <v>25</v>
@@ -2190,7 +2190,7 @@
         <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
         <v>16</v>
@@ -2226,85 +2226,85 @@
         <v>32</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>19.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>18</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
-        <v>16.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>5.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
         <v>4.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,41 +2316,41 @@
         <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT7" t="n">
         <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
         <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA7" t="n">
         <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -2399,13 +2399,13 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
@@ -2414,25 +2414,25 @@
         <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
         <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
         <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X8" t="n">
         <v>70</v>
@@ -2447,7 +2447,7 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
         <v>15</v>
@@ -2489,16 +2489,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
@@ -2507,10 +2507,10 @@
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2519,25 +2519,25 @@
         <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="BG8" t="n">
         <v>5.8</v>
@@ -2546,7 +2546,7 @@
         <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2558,13 +2558,13 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
         <v>4.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
         <v>10.5</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -2638,64 +2638,64 @@
         <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="I9" t="n">
         <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
         <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
         <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
@@ -2740,10 +2740,10 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.4</v>
@@ -2752,7 +2752,7 @@
         <v>9.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2761,79 +2761,79 @@
         <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="BC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG9" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.7</v>
       </c>
       <c r="BU9" t="n">
         <v>3.5</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -2901,10 +2901,10 @@
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
         <v>2.14</v>
@@ -3152,31 +3152,31 @@
         <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P11" t="n">
         <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3185,34 +3185,34 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X11" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>26</v>
       </c>
       <c r="Z11" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
         <v>970</v>
@@ -3227,7 +3227,7 @@
         <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
@@ -3236,7 +3236,7 @@
         <v>140</v>
       </c>
       <c r="AK11" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
@@ -3245,7 +3245,7 @@
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
@@ -3254,55 +3254,55 @@
         <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG11" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>2.6</v>
@@ -3311,7 +3311,7 @@
         <v>2.24</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
         <v>7.2</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
@@ -3332,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
         <v>500</v>
@@ -3460,10 +3460,10 @@
         <v>500</v>
       </c>
       <c r="AA12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB12" t="n">
         <v>500</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>27</v>
       </c>
       <c r="AC12" t="n">
         <v>42</v>
@@ -3475,10 +3475,10 @@
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AH12" t="n">
         <v>95</v>
@@ -3487,7 +3487,7 @@
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
         <v>970</v>
@@ -3505,122 +3505,122 @@
         <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.82</v>
+        <v>2.04</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="AY12" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>1.97</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>4.1</v>
       </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>970</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H13" t="n">
         <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
@@ -3672,7 +3672,7 @@
         <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
         <v>6.4</v>
@@ -3687,7 +3687,7 @@
         <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
         <v>2.26</v>
@@ -3699,10 +3699,10 @@
         <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
@@ -3759,58 +3759,58 @@
         <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
         <v>7</v>
       </c>
       <c r="AS13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY13" t="n">
         <v>8</v>
       </c>
-      <c r="AT13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>14.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BF13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG13" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.8</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -3905,148 +3905,148 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="G14" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
         <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY14" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>55</v>
@@ -4058,77 +4058,77 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG14" t="n">
         <v>12</v>
       </c>
-      <c r="BF14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>7.6</v>
       </c>
-      <c r="BO14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX14" t="n">
         <v>28</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ14" t="n">
         <v>23</v>
       </c>
       <c r="CA14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -881,16 +881,16 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R2" t="n">
         <v>1.74</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
         <v>3.85</v>
@@ -1126,67 +1126,67 @@
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.6</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.51</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="X3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
         <v>500</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>370</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1198,13 +1198,13 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1219,7 +1219,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
@@ -1228,55 +1228,55 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.54</v>
+        <v>8.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,35 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.49</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.26</v>
@@ -1392,19 +1392,19 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1419,124 +1419,124 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
         <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH5" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>11</v>
       </c>
-      <c r="AD5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="AS5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>600</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
-        <v>1.08</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>870</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.08</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
@@ -1900,19 +1900,19 @@
         <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>1.9</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1927,112 +1927,112 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T7" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>44</v>
       </c>
       <c r="AB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="n">
         <v>16</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AI7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -2381,124 +2381,124 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="X8" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
@@ -2507,10 +2507,10 @@
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2519,40 +2519,40 @@
         <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="n">
         <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,16 +2561,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2579,32 +2579,32 @@
         <v>7.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -2635,61 +2635,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
         <v>2.02</v>
       </c>
       <c r="I9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
         <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
         <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
         <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W9" t="n">
         <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
         <v>7.6</v>
@@ -2701,22 +2701,22 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>500</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
         <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
         <v>500</v>
@@ -2743,7 +2743,7 @@
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.4</v>
@@ -2752,7 +2752,7 @@
         <v>9.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2761,61 +2761,61 @@
         <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AY9" t="n">
         <v>7.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BD9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO9" t="n">
         <v>4.8</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BT9" t="n">
         <v>4.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>990</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.49</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
         <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -3170,13 +3170,13 @@
         <v>2.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
         <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3185,43 +3185,43 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
         <v>11.5</v>
@@ -3233,7 +3233,7 @@
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK11" t="n">
         <v>85</v>
@@ -3245,128 +3245,128 @@
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="BB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF11" t="n">
         <v>11</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7</v>
-      </c>
       <c r="BH11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.24</v>
+        <v>6.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO11" t="n">
         <v>3.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.14</v>
+        <v>6.6</v>
       </c>
       <c r="BT11" t="n">
         <v>8</v>
       </c>
       <c r="BU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
         <v>6</v>
       </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.16</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
         <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
@@ -3424,37 +3424,37 @@
         <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="Z12" t="n">
         <v>500</v>
@@ -3466,28 +3466,28 @@
         <v>500</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK12" t="n">
         <v>970</v>
@@ -3499,76 +3499,76 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AO12" t="n">
         <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.04</v>
+        <v>2.86</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.04</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.97</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,50 +3577,50 @@
         <v>5.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO12" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.26</v>
@@ -3678,34 +3678,34 @@
         <v>6.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
         <v>2.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
         <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V13" t="n">
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y13" t="n">
         <v>29</v>
@@ -3726,7 +3726,7 @@
         <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
         <v>18</v>
@@ -3762,46 +3762,46 @@
         <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW13" t="n">
         <v>7</v>
       </c>
-      <c r="AS13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AX13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE13" t="n">
         <v>7.2</v>
@@ -3810,7 +3810,7 @@
         <v>4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="I14" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3932,13 +3932,13 @@
         <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
@@ -3947,34 +3947,34 @@
         <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
         <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
@@ -3983,43 +3983,43 @@
         <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
         <v>21</v>
@@ -4031,22 +4031,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX14" t="n">
         <v>26</v>
       </c>
       <c r="AY14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>55</v>
@@ -4058,77 +4058,77 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
         <v>32</v>
       </c>
       <c r="BG14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT14" t="n">
         <v>4.9</v>
       </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO14" t="n">
+      <c r="BU14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW14" t="n">
         <v>5.8</v>
       </c>
-      <c r="BP14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BX14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>23</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
         <v>5.3</v>
@@ -869,7 +869,7 @@
         <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>5.7</v>
@@ -881,25 +881,25 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="S2" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -1135,7 +1135,7 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
@@ -1144,94 +1144,94 @@
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
@@ -1240,16 +1240,16 @@
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
         <v>10.5</v>
@@ -1258,10 +1258,10 @@
         <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE3" t="n">
         <v>12</v>
@@ -1270,25 +1270,25 @@
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>3.75</v>
+        <v>1.35</v>
       </c>
       <c r="BT3" t="n">
         <v>6.6</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.75</v>
+        <v>1.36</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
         <v>3.25</v>
@@ -1377,16 +1377,16 @@
         <v>2.68</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
@@ -1404,7 +1404,7 @@
         <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1425,25 +1425,25 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1452,79 +1452,79 @@
         <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="BF4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.75</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>9</v>
       </c>
       <c r="AW5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>14</v>
       </c>
-      <c r="AX5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>16</v>
-      </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.21</v>
@@ -1897,7 +1897,7 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.11</v>
@@ -1909,10 +1909,10 @@
         <v>1.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1936,7 +1936,7 @@
         <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>950</v>
@@ -1963,7 +1963,7 @@
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
@@ -1972,7 +1972,7 @@
         <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>600</v>
@@ -1981,64 +1981,64 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.21</v>
+        <v>2.12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.19</v>
+        <v>2.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.21</v>
+        <v>2.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.18</v>
+        <v>2.74</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.19</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.21</v>
+        <v>2.64</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.19</v>
+        <v>2.62</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.21</v>
+        <v>2.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.2</v>
+        <v>2.58</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.21</v>
+        <v>2.88</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.21</v>
+        <v>2.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
         <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
@@ -2160,7 +2160,7 @@
         <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.51</v>
@@ -2169,19 +2169,19 @@
         <v>2.72</v>
       </c>
       <c r="T7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
         <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
         <v>15</v>
@@ -2196,13 +2196,13 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
         <v>20</v>
@@ -2226,13 +2226,13 @@
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
         <v>18.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>18</v>
@@ -2244,19 +2244,19 @@
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
         <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AX7" t="n">
         <v>16</v>
@@ -2268,19 +2268,19 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BF7" t="n">
         <v>15.5</v>
@@ -2289,7 +2289,7 @@
         <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI7" t="n">
         <v>3.05</v>
@@ -2298,31 +2298,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT7" t="n">
         <v>6.4</v>
@@ -2334,23 +2334,23 @@
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
         <v>30</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>22</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -2381,76 +2381,76 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>5.2</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
         <v>26</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
@@ -2462,7 +2462,7 @@
         <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
@@ -2489,97 +2489,97 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
         <v>8.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT8" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8.6</v>
       </c>
       <c r="BU8" t="n">
         <v>5.1</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -2659,67 +2659,67 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
         <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>27</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2728,7 +2728,7 @@
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="n">
         <v>700</v>
@@ -2737,73 +2737,73 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.4</v>
+        <v>25</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
         <v>6</v>
@@ -2812,28 +2812,28 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BN9" t="n">
         <v>7.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU9" t="n">
         <v>4</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -2889,169 +2889,169 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H10" t="n">
         <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
         <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T10" t="n">
         <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
         <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS10" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI10" t="n">
         <v>2.16</v>
@@ -3060,59 +3060,59 @@
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO10" t="n">
         <v>5.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT10" t="n">
         <v>5.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV10" t="n">
         <v>24</v>
       </c>
       <c r="BW10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>60</v>
       </c>
       <c r="CA10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -3167,10 +3167,10 @@
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P11" t="n">
         <v>1.48</v>
@@ -3188,40 +3188,40 @@
         <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
         <v>11.5</v>
@@ -3236,31 +3236,31 @@
         <v>130</v>
       </c>
       <c r="AK11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AT11" t="n">
         <v>5.5</v>
@@ -3269,70 +3269,70 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>12.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO11" t="n">
         <v>3.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3341,32 +3341,32 @@
         <v>6.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA11" t="n">
         <v>5.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X12" t="n">
         <v>500</v>
@@ -3466,16 +3466,16 @@
         <v>500</v>
       </c>
       <c r="AC12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
         <v>19</v>
@@ -3490,7 +3490,7 @@
         <v>180</v>
       </c>
       <c r="AK12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,34 +3499,34 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AT12" t="n">
         <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3535,49 +3535,49 @@
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
         <v>6.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.6</v>
+        <v>1.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO12" t="n">
         <v>4.2</v>
@@ -3586,41 +3586,41 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.65</v>
+        <v>1.67</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -3651,31 +3651,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
@@ -3684,37 +3684,37 @@
         <v>2.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U13" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
         <v>48</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB13" t="n">
         <v>17</v>
@@ -3723,25 +3723,25 @@
         <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
         <v>18</v>
@@ -3750,40 +3750,40 @@
         <v>26</v>
       </c>
       <c r="AM13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN13" t="n">
         <v>7.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AS13" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AV13" t="n">
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
@@ -3792,10 +3792,10 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
         <v>14.5</v>
@@ -3804,77 +3804,77 @@
         <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.5</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU13" t="n">
         <v>4.6</v>
       </c>
       <c r="BV13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>14</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="I14" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3932,121 +3932,121 @@
         <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
         <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AG14" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI14" t="n">
         <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP14" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
         <v>9.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX14" t="n">
         <v>26</v>
       </c>
       <c r="AY14" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
         <v>55</v>
@@ -4058,13 +4058,13 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF14" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="n">
         <v>3.75</v>
@@ -4073,62 +4073,62 @@
         <v>2.98</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BQ14" t="n">
         <v>8</v>
       </c>
       <c r="BR14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX14" t="n">
         <v>27</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
         <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>5.7</v>
@@ -881,31 +881,31 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R2" t="n">
         <v>1.77</v>
       </c>
       <c r="S2" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W2" t="n">
         <v>1.23</v>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>48</v>
@@ -968,61 +968,61 @@
         <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
         <v>5.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
         <v>5.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB2" t="n">
         <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD2" t="n">
         <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BH2" t="n">
         <v>5.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G3" t="n">
         <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.68</v>
@@ -1177,13 +1177,13 @@
         <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1192,7 +1192,7 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
@@ -1207,7 +1207,7 @@
         <v>85</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM3" t="n">
         <v>500</v>
@@ -1219,7 +1219,7 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
@@ -1231,13 +1231,13 @@
         <v>15</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -1246,31 +1246,31 @@
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BH3" t="n">
         <v>2.84</v>
@@ -1282,7 +1282,7 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
         <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
@@ -1401,7 +1401,7 @@
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
         <v>2.4</v>
@@ -1467,64 +1467,64 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC4" t="n">
         <v>3.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.05</v>
       </c>
       <c r="BD4" t="n">
         <v>3.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="I5" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="J5" t="n">
         <v>4.2</v>
@@ -1637,115 +1637,115 @@
         <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>500</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL5" t="n">
         <v>160</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1754,95 +1754,95 @@
         <v>27</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>28</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.76</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BN5" t="n">
         <v>9.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
         <v>11</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BX5" t="n">
         <v>21</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.21</v>
@@ -1897,28 +1897,28 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q6" t="n">
         <v>1.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
         <v>1.89</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1942,10 +1942,10 @@
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1954,10 +1954,10 @@
         <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1975,64 +1975,64 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.68</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.74</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
         <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.64</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.44</v>
+        <v>5.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.14</v>
+        <v>3.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.92</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2044,7 +2044,7 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,47 +2056,47 @@
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
         <v>2.88</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
         <v>2.52</v>
@@ -2178,19 +2178,19 @@
         <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
@@ -2211,22 +2211,22 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>38</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN7" t="n">
         <v>18.5</v>
@@ -2235,10 +2235,10 @@
         <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
@@ -2247,10 +2247,10 @@
         <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
@@ -2274,25 +2274,25 @@
         <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BF7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
@@ -2310,16 +2310,16 @@
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
         <v>7.2</v>
@@ -2328,7 +2328,7 @@
         <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>21</v>
@@ -2337,20 +2337,20 @@
         <v>6.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -2402,7 +2402,7 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
         <v>6</v>
@@ -2411,34 +2411,34 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y8" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,7 +2447,7 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
         <v>15</v>
@@ -2456,22 +2456,22 @@
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2483,7 +2483,7 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2507,10 +2507,10 @@
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2522,7 +2522,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2534,10 +2534,10 @@
         <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
         <v>8.800000000000001</v>
@@ -2549,28 +2549,28 @@
         <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2579,10 +2579,10 @@
         <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2600,11 +2600,11 @@
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I9" t="n">
         <v>2.1</v>
@@ -2650,7 +2650,7 @@
         <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -2668,7 +2668,7 @@
         <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2683,7 +2683,7 @@
         <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2698,10 +2698,10 @@
         <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
         <v>8</v>
@@ -2710,40 +2710,40 @@
         <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AL9" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.2</v>
@@ -2752,7 +2752,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2764,37 +2764,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>65</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH9" t="n">
         <v>2.96</v>
@@ -2806,7 +2806,7 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>7.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA9" t="n">
         <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -2889,46 +2889,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T10" t="n">
         <v>2.06</v>
@@ -2937,40 +2937,40 @@
         <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
         <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
         <v>80</v>
@@ -2994,7 +2994,7 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>6.4</v>
@@ -3003,7 +3003,7 @@
         <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
         <v>14.5</v>
@@ -3030,22 +3030,22 @@
         <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
         <v>8.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
         <v>5.1</v>
@@ -3161,46 +3161,46 @@
         <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
         <v>1.61</v>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T11" t="n">
         <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
         <v>95</v>
@@ -3209,19 +3209,19 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
         <v>11.5</v>
@@ -3230,13 +3230,13 @@
         <v>85</v>
       </c>
       <c r="AI11" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="AJ11" t="n">
         <v>130</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="n">
         <v>460</v>
@@ -3251,28 +3251,28 @@
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
@@ -3284,28 +3284,28 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF11" t="n">
         <v>27</v>
       </c>
       <c r="BG11" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BI11" t="n">
         <v>2.38</v>
@@ -3314,13 +3314,13 @@
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
@@ -3332,41 +3332,41 @@
         <v>18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT11" t="n">
         <v>7.8</v>
       </c>
       <c r="BU11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
         <v>5.6</v>
       </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="n">
         <v>5.2</v>
@@ -3412,7 +3412,7 @@
         <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
@@ -3436,7 +3436,7 @@
         <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.56</v>
@@ -3448,7 +3448,7 @@
         <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
         <v>500</v>
@@ -3499,10 +3499,10 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
         <v>8.199999999999999</v>
@@ -3511,22 +3511,22 @@
         <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>7.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3538,43 +3538,43 @@
         <v>6.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
         <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
         <v>7.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BF12" t="n">
         <v>3.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="n">
         <v>5</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="BN12" t="n">
         <v>4.9</v>
@@ -3583,10 +3583,10 @@
         <v>4.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3595,22 +3595,22 @@
         <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
@@ -3675,31 +3675,31 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
         <v>1.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
         <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>2.24</v>
@@ -3714,10 +3714,10 @@
         <v>48</v>
       </c>
       <c r="AA13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC13" t="n">
         <v>12.5</v>
@@ -3729,16 +3729,16 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
         <v>18</v>
@@ -3747,134 +3747,134 @@
         <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
         <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT13" t="n">
         <v>9</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -3908,25 +3908,25 @@
         <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I14" t="n">
         <v>1.87</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
         <v>4.2</v>
@@ -3938,7 +3938,7 @@
         <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.43</v>
@@ -3947,16 +3947,16 @@
         <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
         <v>2.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3974,22 +3974,22 @@
         <v>18</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF14" t="n">
         <v>38</v>
       </c>
       <c r="AG14" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>34</v>
@@ -4004,13 +4004,13 @@
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
         <v>60</v>
       </c>
       <c r="AO14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
         <v>14.5</v>
@@ -4022,7 +4022,7 @@
         <v>10</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT14" t="n">
         <v>15.5</v>
@@ -4034,10 +4034,10 @@
         <v>9.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AY14" t="n">
         <v>16.5</v>
@@ -4049,19 +4049,19 @@
         <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BC14" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BD14" t="n">
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="BF14" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BG14" t="n">
         <v>10</v>
@@ -4076,59 +4076,59 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT14" t="n">
         <v>4.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV14" t="n">
         <v>13</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX14" t="n">
         <v>27</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,13 +863,13 @@
         <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
         <v>5.7</v>
@@ -881,19 +881,19 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S2" t="n">
         <v>1.87</v>
@@ -902,10 +902,10 @@
         <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W2" t="n">
         <v>1.23</v>
@@ -956,7 +956,7 @@
         <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN2" t="n">
         <v>29</v>
@@ -965,19 +965,19 @@
         <v>6</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR2" t="n">
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
         <v>5.7</v>
@@ -989,40 +989,40 @@
         <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
         <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BH2" t="n">
         <v>5.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1114,97 +1114,97 @@
         <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
         <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
         <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
         <v>290</v>
@@ -1213,73 +1213,73 @@
         <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
         <v>15</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AX3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
         <v>6</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.35</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1365,52 +1365,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.25</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="U4" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1470,22 +1470,22 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
         <v>4.3</v>
@@ -1494,101 +1494,101 @@
         <v>5.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.1</v>
+        <v>2.94</v>
       </c>
       <c r="AZ4" t="n">
         <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="BD4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
         <v>3.7</v>
       </c>
-      <c r="BE4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G5" t="n">
         <v>4.3</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="H5" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
         <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB5" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>120</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15</v>
-      </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AY5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>32</v>
       </c>
-      <c r="BE5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF5" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
         <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1873,52 +1873,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>15.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.11</v>
       </c>
-      <c r="P6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="U6" t="n">
-        <v>3.15</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1957,7 +1957,7 @@
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1975,73 +1975,73 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.4</v>
+        <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>1.73</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AV6" t="n">
         <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>1.76</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>1.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>1.76</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>1.74</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK6" t="n">
         <v>4.4</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.52</v>
+        <v>5.7</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.38</v>
+        <v>6.2</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.27</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
         <v>2.52</v>
       </c>
       <c r="V7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.53</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.57</v>
-      </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
         <v>22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX7" t="n">
         <v>17.5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>16</v>
-      </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW7" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
         <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K8" t="n">
         <v>5.1</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.2</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
@@ -2414,31 +2414,31 @@
         <v>2.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S8" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>75</v>
       </c>
       <c r="Y8" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2453,10 +2453,10 @@
         <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE8" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
         <v>25</v>
@@ -2471,7 +2471,7 @@
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2483,7 +2483,7 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2495,82 +2495,82 @@
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
         <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2579,32 +2579,32 @@
         <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
         <v>2.02</v>
@@ -2650,40 +2650,40 @@
         <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2692,70 +2692,70 @@
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
         <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AF9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="n">
         <v>700</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2767,98 +2767,98 @@
         <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BE9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
         <v>4.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -2892,91 +2892,91 @@
         <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="J10" t="n">
         <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
         <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="AI10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>900</v>
@@ -2997,52 +2997,52 @@
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
         <v>14.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
         <v>16</v>
       </c>
       <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>19</v>
       </c>
-      <c r="AY10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
         <v>6.8</v>
@@ -3051,68 +3051,68 @@
         <v>8.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
         <v>7.2</v>
       </c>
-      <c r="BO10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BT10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>7</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -3143,40 +3143,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
         <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3185,73 +3185,73 @@
         <v>6.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
         <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y11" t="n">
         <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
         <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>460</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
@@ -3260,37 +3260,37 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
         <v>40</v>
@@ -3299,74 +3299,74 @@
         <v>38</v>
       </c>
       <c r="BF11" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I12" t="n">
         <v>6.2</v>
@@ -3412,58 +3412,58 @@
         <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12" t="n">
         <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
         <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
         <v>42</v>
@@ -3481,16 +3481,16 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,34 +3499,34 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AR12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS12" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3535,99 +3535,99 @@
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.76</v>
+        <v>6.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="n">
         <v>5</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.16</v>
+        <v>5.3</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BT12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2</v>
+        <v>2.86</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club ABB</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I13" t="n">
         <v>4.4</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.78</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BT13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>9</v>
-      </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9</v>
+        <v>2.52</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9</v>
+        <v>2.56</v>
       </c>
       <c r="BZ13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.4</v>
+        <v>2.46</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,1006 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Birmingham Legion FC</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Louisville FC</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AB14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH14" t="n">
         <v>18</v>
       </c>
-      <c r="AC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22</v>
-      </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AP14" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9.4</v>
       </c>
       <c r="AW14" t="n">
         <v>16.5</v>
       </c>
       <c r="AX14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Club ABB</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X15" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Louisville FC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX16" t="n">
         <v>30</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AY16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB14" t="n">
+      <c r="BA16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>44</v>
       </c>
-      <c r="BC14" t="n">
-        <v>46</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF14" t="n">
+      <c r="AK17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL17" t="n">
         <v>44</v>
       </c>
-      <c r="BG14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>7</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-03 08:12:38</t>
+      <c r="AM17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -884,76 +884,76 @@
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="U2" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Y2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH2" t="n">
         <v>19.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>55</v>
@@ -962,125 +962,125 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BT2" t="n">
         <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1111,184 +1111,184 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.88</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.82</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>65</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI3" t="n">
         <v>2.32</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>5.2</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
@@ -1398,19 +1398,19 @@
         <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U4" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1434,7 +1434,7 @@
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1470,125 +1470,125 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
         <v>2.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AV4" t="n">
         <v>5.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="AZ4" t="n">
         <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE4" t="n">
         <v>3</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.45</v>
+        <v>2.22</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.62</v>
+        <v>1.37</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1619,67 +1619,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="I5" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
         <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
         <v>22</v>
@@ -1688,7 +1688,7 @@
         <v>23</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>11.5</v>
@@ -1709,19 +1709,19 @@
         <v>46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AO5" t="n">
         <v>8.4</v>
@@ -1742,16 +1742,16 @@
         <v>18.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW5" t="n">
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY5" t="n">
         <v>15</v>
@@ -1763,25 +1763,25 @@
         <v>18.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
         <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG5" t="n">
         <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI5" t="n">
         <v>3.45</v>
@@ -1790,13 +1790,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
         <v>8.4</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU5" t="n">
         <v>3.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
         <v>22</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>15</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1873,52 +1873,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I6" t="n">
-        <v>15.5</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
         <v>3.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="R6" t="n">
         <v>2.06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1927,13 +1927,13 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA6" t="n">
         <v>500</v>
@@ -1942,10 +1942,10 @@
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1957,7 +1957,7 @@
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1975,25 +1975,25 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.74</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.73</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.73</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.74</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
         <v>5.5</v>
@@ -2002,10 +2002,10 @@
         <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.76</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.75</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
         <v>5.5</v>
@@ -2014,67 +2014,67 @@
         <v>5.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.76</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
         <v>8.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH6" t="n">
         <v>6</v>
       </c>
-      <c r="BG6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BI6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU6" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2089,14 +2089,14 @@
         <v>6.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2127,142 +2127,142 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
         <v>22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AT7" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>12</v>
@@ -2271,7 +2271,7 @@
         <v>22</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
@@ -2280,22 +2280,22 @@
         <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
         <v>7.2</v>
@@ -2304,22 +2304,22 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS7" t="n">
         <v>7.4</v>
@@ -2328,29 +2328,29 @@
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BW7" t="n">
         <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CA7" t="n">
         <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G8" t="n">
         <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.25</v>
@@ -2405,34 +2405,34 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>75</v>
@@ -2453,13 +2453,13 @@
         <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
@@ -2471,10 +2471,10 @@
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>75</v>
@@ -2483,7 +2483,7 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2495,22 +2495,22 @@
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
         <v>8.199999999999999</v>
@@ -2519,10 +2519,10 @@
         <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2537,74 +2537,74 @@
         <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="n">
         <v>5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.8</v>
+        <v>2.72</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2635,124 +2635,124 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.02</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z9" t="n">
         <v>11</v>
       </c>
-      <c r="Y9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AA9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB9" t="n">
         <v>13.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
         <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL9" t="n">
         <v>110</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>90</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>22</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2761,25 +2761,25 @@
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>22</v>
       </c>
-      <c r="AX9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19</v>
-      </c>
       <c r="BA9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BC9" t="n">
         <v>55</v>
@@ -2788,77 +2788,77 @@
         <v>65</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
       </c>
       <c r="BO9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.7</v>
       </c>
       <c r="BU9" t="n">
         <v>3.95</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>38</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>38</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
         <v>3.4</v>
@@ -2898,31 +2898,31 @@
         <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
         <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.15</v>
@@ -2937,40 +2937,40 @@
         <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
         <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
         <v>27</v>
@@ -2979,10 +2979,10 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL10" t="n">
         <v>540</v>
@@ -3000,55 +3000,55 @@
         <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
         <v>6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.5</v>
       </c>
       <c r="AV10" t="n">
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX10" t="n">
         <v>16</v>
       </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BH10" t="n">
         <v>2.76</v>
@@ -3066,16 +3066,16 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN10" t="n">
         <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.6</v>
@@ -3084,13 +3084,13 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV10" t="n">
         <v>26</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
         <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -3167,7 +3167,7 @@
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
         <v>1.62</v>
@@ -3176,7 +3176,7 @@
         <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3185,31 +3185,31 @@
         <v>6.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
         <v>7.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -3227,13 +3227,13 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI11" t="n">
         <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
         <v>34</v>
@@ -3263,19 +3263,19 @@
         <v>16</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -3293,13 +3293,13 @@
         <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG11" t="n">
         <v>11.5</v>
@@ -3308,10 +3308,10 @@
         <v>2.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
         <v>7</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>220</v>
       </c>
       <c r="BN11" t="n">
         <v>4.6</v>
@@ -3332,41 +3332,41 @@
         <v>18.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>48</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
         <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.14</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R12" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3466,7 +3466,7 @@
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
@@ -3475,10 +3475,10 @@
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>970</v>
@@ -3487,10 +3487,10 @@
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,19 +3499,19 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.2</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
         <v>4.2</v>
@@ -3520,13 +3520,13 @@
         <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3535,92 +3535,92 @@
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -3654,64 +3654,64 @@
         <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.3</v>
       </c>
       <c r="P13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="X13" t="n">
         <v>17</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
         <v>85</v>
@@ -3723,16 +3723,16 @@
         <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>20</v>
@@ -3753,94 +3753,94 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BA13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6</v>
       </c>
-      <c r="AT13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3849,7 +3849,7 @@
         <v>2.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU13" t="n">
         <v>4.5</v>
@@ -3858,23 +3858,23 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.46</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I14" t="n">
         <v>2.46</v>
@@ -3929,7 +3929,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
@@ -3941,40 +3941,40 @@
         <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
         <v>13</v>
@@ -3998,43 +3998,43 @@
         <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
         <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
         <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX14" t="n">
         <v>19.5</v>
@@ -4043,25 +4043,25 @@
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
         <v>10.5</v>
@@ -4070,7 +4070,7 @@
         <v>4.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.6</v>
@@ -4091,7 +4091,7 @@
         <v>5.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ14" t="n">
         <v>5.9</v>
@@ -4103,7 +4103,7 @@
         <v>6.2</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU14" t="n">
         <v>4.3</v>
@@ -4121,14 +4121,14 @@
         <v>6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA14" t="n">
         <v>5.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G15" t="n">
         <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
         <v>4.9</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -4186,7 +4186,7 @@
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
         <v>2.74</v>
@@ -4207,7 +4207,7 @@
         <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
         <v>2.24</v>
@@ -4243,7 +4243,7 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
         <v>48</v>
@@ -4270,13 +4270,13 @@
         <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR15" t="n">
         <v>7.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -4294,7 +4294,7 @@
         <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>12.5</v>
@@ -4303,7 +4303,7 @@
         <v>7.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>14.5</v>
@@ -4312,13 +4312,13 @@
         <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BH15" t="n">
         <v>4.9</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.36</v>
@@ -4452,19 +4452,19 @@
         <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
         <v>18</v>
@@ -4476,25 +4476,25 @@
         <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>18.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
@@ -4503,22 +4503,22 @@
         <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AK16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL16" t="n">
         <v>55</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>60</v>
       </c>
       <c r="AM16" t="n">
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP16" t="n">
         <v>15.5</v>
@@ -4530,7 +4530,7 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -4545,25 +4545,25 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
         <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BC16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BD16" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="BE16" t="n">
         <v>48</v>
@@ -4572,7 +4572,7 @@
         <v>38</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="n">
         <v>3.85</v>
@@ -4584,59 +4584,59 @@
         <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR16" t="n">
         <v>46</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT16" t="n">
         <v>4.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV16" t="n">
         <v>13</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX16" t="n">
         <v>26</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>21</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -4727,7 +4727,7 @@
         <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
         <v>55</v>
@@ -4745,7 +4745,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>970</v>
@@ -4754,7 +4754,7 @@
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>44</v>
@@ -4766,7 +4766,7 @@
         <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
         <v>1000</v>
@@ -4775,122 +4775,122 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AU17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH17" t="n">
         <v>3.45</v>
       </c>
-      <c r="AV17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI17" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.1</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5</v>
+        <v>50</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>2.44</v>
+        <v>50</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>3.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AJ2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.4</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>1.51</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>1.51</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.1</v>
+        <v>1.51</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.4</v>
+        <v>1.51</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>1.51</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.15</v>
+        <v>1.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="K3" t="n">
-        <v>2.98</v>
+        <v>1.83</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>670</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AY3" t="n">
         <v>5.4</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AZ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>250</v>
+      </c>
+      <c r="BC3" t="n">
         <v>32</v>
       </c>
-      <c r="AA3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="BD3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>38</v>
       </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>55</v>
-      </c>
       <c r="BH3" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1365,52 +1365,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2.64</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>8.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1419,176 +1419,176 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>120</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.5</v>
+        <v>1.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>1.18</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.58</v>
+        <v>1.18</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.22</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.32</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.22</v>
+        <v>1.18</v>
       </c>
       <c r="BH4" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V5" t="n">
         <v>4.4</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.06</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>340</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY5" t="n">
         <v>23</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AZ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.32</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>1.58</v>
       </c>
       <c r="AO6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>2.86</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>1.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="U7" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
         <v>21</v>
       </c>
-      <c r="AA7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AX7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AI7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="BD7" t="n">
         <v>22</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>21</v>
-      </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BF7" t="n">
         <v>13</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BO7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BR7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS7" t="n">
         <v>26</v>
       </c>
-      <c r="BS7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BV7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BZ7" t="n">
-        <v>16</v>
+        <v>860</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>2.12</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S8" t="n">
         <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="X8" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" t="n">
         <v>15</v>
       </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17</v>
-      </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>25</v>
       </c>
-      <c r="AI8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
+      <c r="AR8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BJ8" t="n">
         <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.72</v>
+        <v>50</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO8" t="n">
         <v>4.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AE9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
         <v>7</v>
       </c>
-      <c r="Z9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AS9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA9" t="n">
         <v>25</v>
       </c>
-      <c r="AB9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="BB9" t="n">
         <v>10</v>
       </c>
-      <c r="AW9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>50</v>
-      </c>
       <c r="BC9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
         <v>65</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>28</v>
       </c>
       <c r="BF9" t="n">
         <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
         <v>10</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BT9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX9" t="n">
         <v>38</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>38</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -2889,73 +2889,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
         <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R10" t="n">
         <v>1.15</v>
       </c>
       <c r="S10" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
         <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
@@ -2967,13 +2967,13 @@
         <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -3000,10 +3000,10 @@
         <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
         <v>16.5</v>
@@ -3021,16 +3021,16 @@
         <v>23</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
         <v>34</v>
@@ -3045,19 +3045,19 @@
         <v>38</v>
       </c>
       <c r="BF10" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK10" t="n">
         <v>5.2</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO10" t="n">
         <v>5.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
         <v>26</v>
       </c>
       <c r="BW10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
         <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -3167,79 +3167,79 @@
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
         <v>6.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>7.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
       <c r="AH11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
         <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK11" t="n">
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
@@ -3254,16 +3254,16 @@
         <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
@@ -3272,10 +3272,10 @@
         <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -3284,7 +3284,7 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
         <v>18</v>
@@ -3302,13 +3302,13 @@
         <v>14</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH11" t="n">
         <v>2.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="BJ11" t="n">
         <v>12.5</v>
@@ -3332,41 +3332,41 @@
         <v>18.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR11" t="n">
         <v>48</v>
       </c>
       <c r="BS11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
         <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
         <v>1.65</v>
@@ -3406,37 +3406,37 @@
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>870</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="O12" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>2.84</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -3654,67 +3654,67 @@
         <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
         <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
         <v>10.5</v>
@@ -3723,136 +3723,136 @@
         <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI13" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -3905,61 +3905,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.7</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.68</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y14" t="n">
         <v>14</v>
@@ -3980,37 +3980,37 @@
         <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
         <v>14</v>
@@ -4022,13 +4022,13 @@
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
         <v>8.6</v>
@@ -4046,19 +4046,19 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF14" t="n">
         <v>20</v>
@@ -4067,68 +4067,68 @@
         <v>10.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN14" t="n">
         <v>7.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT14" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.8</v>
       </c>
       <c r="BU14" t="n">
         <v>4.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BY14" t="n">
         <v>6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CA14" t="n">
         <v>5.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -4155,26 +4155,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club ABB</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -4183,70 +4183,70 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
         <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
         <v>28</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
         <v>18</v>
@@ -4255,52 +4255,52 @@
         <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR15" t="n">
         <v>7.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
         <v>9.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB15" t="n">
         <v>15</v>
@@ -4309,10 +4309,10 @@
         <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
         <v>6.4</v>
@@ -4342,7 +4342,7 @@
         <v>5.1</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP15" t="n">
         <v>11.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -4419,10 +4419,10 @@
         <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -4431,7 +4431,7 @@
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4446,31 +4446,31 @@
         <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R16" t="n">
         <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.73</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
         <v>12.5</v>
@@ -4485,19 +4485,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE16" t="n">
         <v>18.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>32</v>
@@ -4509,13 +4509,13 @@
         <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO16" t="n">
         <v>11.5</v>
@@ -4545,13 +4545,13 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
         <v>28</v>
@@ -4560,10 +4560,10 @@
         <v>44</v>
       </c>
       <c r="BC16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
         <v>48</v>
@@ -4578,7 +4578,7 @@
         <v>3.85</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
         <v>10</v>
@@ -4614,7 +4614,7 @@
         <v>4.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BV16" t="n">
         <v>13</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G17" t="n">
         <v>2.92</v>
@@ -4676,31 +4676,31 @@
         <v>2.78</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
         <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
         <v>1.32</v>
@@ -4709,16 +4709,16 @@
         <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -4775,10 +4775,10 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AR17" t="n">
         <v>3.6</v>
@@ -4793,16 +4793,16 @@
         <v>3.55</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AW17" t="n">
         <v>3.85</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>3.9</v>
@@ -4850,7 +4850,7 @@
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7</v>
+        <v>1.58</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>1.62</v>
       </c>
       <c r="J2" t="n">
-        <v>1.48</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,43 +881,43 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>75</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S2" t="n">
-        <v>14</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -926,31 +926,31 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.8</v>
+        <v>110</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AH2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>1.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.52</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BA2" t="n">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="BF2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BG2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sacachispas</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AD Berazategui</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.08</v>
       </c>
-      <c r="S3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>200</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>48</v>
-      </c>
       <c r="BG3" t="n">
-        <v>250</v>
+        <v>1.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I4" t="n">
         <v>4.2</v>
       </c>
-      <c r="I4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.94</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
         <v>30</v>
       </c>
       <c r="AA4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
         <v>120</v>
       </c>
-      <c r="AB4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AN4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF4" t="n">
         <v>12</v>
       </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BG4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>9.6</v>
       </c>
-      <c r="AR4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="BK4" t="n">
         <v>6</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>150</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>17.5</v>
+        <v>2.16</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
         <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M5" t="n">
         <v>1.04</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I5" t="n">
-        <v>870</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>950</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>13.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.83</v>
+        <v>5.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6</v>
       </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,114 +1859,114 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forward Madison FC</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="G6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S6" t="n">
         <v>2.26</v>
       </c>
-      <c r="H6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>970</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL6" t="n">
         <v>38</v>
@@ -1975,135 +1975,135 @@
         <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>2.26</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>2.3</v>
       </c>
       <c r="AS6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY6" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>2.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>2.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>2.24</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,99 +2113,99 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Birmingham Legion FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Louisville FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AF7" t="n">
         <v>32</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>29</v>
       </c>
       <c r="AG7" t="n">
         <v>16.5</v>
@@ -2214,150 +2214,150 @@
         <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AK7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV7" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>12</v>
       </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BN7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO7" t="n">
         <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BU7" t="n">
         <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,84 +2367,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boliviano</t>
+          <t>Portland Hearts of Pine</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.52</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
@@ -2456,10 +2456,10 @@
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
@@ -2468,651 +2468,143 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.22</v>
+        <v>3.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.32</v>
+        <v>3.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.18</v>
+        <v>4.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.92</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Birmingham Legion FC</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Louisville FC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-03 16:43:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Corpus Christi</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Portland Hearts of Pine</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X10" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1.62</v>
+        <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S2" t="n">
-        <v>75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>110</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>46</v>
-      </c>
       <c r="BG2" t="n">
-        <v>50</v>
+        <v>1.25</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,72 +1097,72 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.11</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1177,164 +1177,164 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.25</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.25</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.25</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.25</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.25</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.25</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.25</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.25</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.25</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.25</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.25</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.25</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.25</v>
+        <v>40</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>FC Naples</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Forward Madison FC</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>2.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI4" t="n">
         <v>24</v>
       </c>
-      <c r="Y4" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
         <v>50</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.5</v>
+        <v>38</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG4" t="n">
         <v>7</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BX4" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AW5" t="n">
         <v>2.32</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AX5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
         <v>1.04</v>
       </c>
-      <c r="N5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X5" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BJ5" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Birmingham Legion FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boliviano</t>
+          <t>Louisville FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>4.5</v>
       </c>
       <c r="H6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
         <v>4.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>1.26</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.16</v>
-      </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>90</v>
       </c>
-      <c r="AF6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>970</v>
-      </c>
       <c r="AK6" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF6" t="n">
         <v>38</v>
       </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BG6" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>70</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,498 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Birmingham Legion FC</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Louisville FC</t>
+          <t>Portland Hearts of Pine</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.98</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>950</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>2.94</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>10</v>
-      </c>
       <c r="BT7" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>2.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Corpus Christi</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Portland Hearts of Pine</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Forward Madison FC</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>2.26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>2.26</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>2.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.5</v>
+        <v>2.22</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>2.32</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>2.18</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>2.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>2.32</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>2.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>2.24</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>2.32</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>1.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>40</v>
+        <v>2.3</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Naples</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Portland Hearts of Pine</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="H4" t="n">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>1.96</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1389,968 +1389,206 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.48</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>1.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.4</v>
+        <v>1.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.2</v>
+        <v>1.69</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>1.69</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.5</v>
+        <v>1.69</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>32</v>
+        <v>1.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>1.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>1.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>28</v>
+        <v>1.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Real Potosi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Academia de Balompie Boliviano</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-03 20:58:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Birmingham Legion FC</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Louisville FC</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>110</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-03 20:58:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Corpus Christi</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Portland Hearts of Pine</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>950</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
